--- a/calculation_forms/029_physics_formula_calculator--calculation_forms.xlsx
+++ b/calculation_forms/029_physics_formula_calculator--calculation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mass',_'value':_'mass'}</t>
+          <t>mass</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'mass', 'value': 'mass'}</t>
+          <t>mass</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'acceleration',_'value':_'acceleration'}</t>
+          <t>acceleration</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'acceleration', 'value': 'acceleration'}</t>
+          <t>acceleration</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'gravity',_'value':_'gravity'}</t>
+          <t>gravity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'gravity', 'value': 'gravity'}</t>
+          <t>gravity</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'distance',_'value':_'distance'}</t>
+          <t>distance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'distance', 'value': 'distance'}</t>
+          <t>distance</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'time',_'value':_'time'}</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'time', 'value': 'time'}</t>
+          <t>time</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mass_constant',_'value':_'mass_constant'}</t>
+          <t>mass_constant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'mass constant', 'value': 'mass constant'}</t>
+          <t>mass constant</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'acceleration_constant',_'value':_'acceleration_constant'}</t>
+          <t>acceleration_constant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'acceleration constant', 'value': 'acceleration constant'}</t>
+          <t>acceleration constant</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'constant_speed',_'value':_'constant_speed'}</t>
+          <t>constant_speed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'constant speed', 'value': 'constant speed'}</t>
+          <t>constant speed</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'constant_acceleration',_'value':_'constant_acceleration'}</t>
+          <t>constant_acceleration</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'constant acceleration', 'value': 'constant acceleration'}</t>
+          <t>constant acceleration</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
